--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486713_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486713_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.847</v>
+        <v>5.5753</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0788</v>
+        <v>5.0305</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7682</v>
+        <v>0.5447</v>
       </c>
       <c r="G2" t="n">
         <v>2.2068</v>
@@ -610,13 +610,13 @@
         <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>0.32</v>
+        <v>0.0483</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2753</v>
+        <v>0.2271</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0447</v>
+        <v>-0.1788</v>
       </c>
       <c r="V2" t="n">
         <v>2.741</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9039</v>
+        <v>3.9024</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9549</v>
+        <v>2.3756</v>
       </c>
       <c r="F3" t="n">
-        <v>1.949</v>
+        <v>1.5269</v>
       </c>
       <c r="G3" t="n">
         <v>3.5809</v>
@@ -688,13 +688,13 @@
         <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5844</v>
+        <v>-0.5859</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4142</v>
+        <v>0.0065</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1702</v>
+        <v>-0.5924</v>
       </c>
       <c r="V3" t="n">
         <v>0.3282</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
+        <v>1.8447</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="F4" t="n">
         <v>1.4681</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.2732</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.1949</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0378</v>
@@ -766,13 +766,13 @@
         <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.618</v>
+        <v>-0.2414</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.221</v>
+        <v>-0.1175</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.397</v>
+        <v>-0.1239</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. HERNÁNDEZ TRUJILLO</t>
+          <t>J. MOLINA MELENDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5497</v>
+        <v>-0.0615</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6161</v>
+        <v>0.8777</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0665</v>
+        <v>-0.9391</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2448</v>
+        <v>1.7518</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5999</v>
+        <v>-0.0207</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8447</v>
+        <v>1.7724</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7125</v>
+        <v>2.7738</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1524</v>
+        <v>1.7043</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.865</v>
+        <v>1.0694</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5322</v>
+        <v>-1.022</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5525</v>
+        <v>-1.725</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0203</v>
+        <v>0.703</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1931</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9308</v>
+        <v>-3.8616</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7377</v>
+        <v>2.1239</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2317</v>
+        <v>-1.3032</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7995</v>
+        <v>-0.4899</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5678</v>
+        <v>-0.8133</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6565</v>
+        <v>1.2277</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2277</v>
+        <v>2.4554</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5712</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MOLINA MELENDEZ</t>
+          <t>A. BIURRUN SANTAMARIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6504</v>
+        <v>-0.8666</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5122</v>
+        <v>1.4607</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1626</v>
+        <v>-2.3273</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7518</v>
+        <v>-0.5602</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0207</v>
+        <v>-1.5933</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7724</v>
+        <v>1.0331</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7738</v>
+        <v>1.3642</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7043</v>
+        <v>0.0621</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0694</v>
+        <v>1.3022</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.022</v>
+        <v>-1.9244</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.725</v>
+        <v>-1.6554</v>
       </c>
       <c r="O6" t="n">
-        <v>0.703</v>
+        <v>-0.269</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.7377</v>
+        <v>0.3862</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1239</v>
+        <v>0.3862</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8922</v>
+        <v>0.2068</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8554</v>
+        <v>0.0965</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0368</v>
+        <v>0.1104</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2277</v>
+        <v>-0.8995</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2277</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BIURRUN SANTAMARIA</t>
+          <t>J. HERNÁNDEZ TRUJILLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9741</v>
+        <v>-1.2433</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2539</v>
+        <v>-1.2849</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.228</v>
+        <v>0.0416</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5602</v>
+        <v>-1.2448</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5933</v>
+        <v>0.5999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0331</v>
+        <v>-1.8447</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3642</v>
+        <v>-0.7125</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0621</v>
+        <v>1.1524</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3022</v>
+        <v>-1.865</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9244</v>
+        <v>-0.5322</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6554</v>
+        <v>-0.5525</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.269</v>
+        <v>0.0203</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3862</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3862</v>
+        <v>1.7377</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0993</v>
+        <v>-0.4619</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1104</v>
+        <v>0.1307</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2097</v>
+        <v>-0.5926</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8995</v>
+        <v>0.6565</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8995</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8536</v>
+        <v>-1.9033</v>
       </c>
       <c r="E8" t="n">
         <v>-2.5718</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.6686</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2412</v>
@@ -1078,13 +1078,13 @@
         <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>0.353</v>
+        <v>0.3034</v>
       </c>
       <c r="T8" t="n">
         <v>0.193</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1601</v>
+        <v>0.1104</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2417</v>
+        <v>-2.5271</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3311</v>
+        <v>-0.6414</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9106</v>
+        <v>-1.8858</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4138</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6509</v>
+        <v>0.3654</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6343</v>
+        <v>0.324</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5133</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9079</v>
+        <v>-2.8609</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3706</v>
+        <v>0.2189</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.2784</v>
+        <v>-3.0798</v>
       </c>
       <c r="G10" t="n">
         <v>0.3353</v>
@@ -1234,13 +1234,13 @@
         <v>1.5446</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1161</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4685</v>
+        <v>0.3169</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5846</v>
+        <v>-0.3859</v>
       </c>
       <c r="V10" t="n">
         <v>-2.741</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2536</v>
+        <v>-2.866</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4511</v>
+        <v>-1.2373</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8025</v>
+        <v>-1.6286</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6994</v>
@@ -1312,13 +1312,13 @@
         <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1254</v>
+        <v>-0.7378</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0004</v>
+        <v>0.2134</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1251</v>
+        <v>-0.9512</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6565</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0929</v>
+        <v>-4.7468</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.7045</v>
+        <v>-5.2838</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6115</v>
+        <v>0.537</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9889</v>
@@ -1390,13 +1390,13 @@
         <v>1.3515</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5941</v>
+        <v>-1.2479</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6347</v>
+        <v>-0.214</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9594</v>
+        <v>-1.0339</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.304899999999998</v>
+        <v>-5.753100000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.231000000000001</v>
+        <v>-0.6791999999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.073799999999999</v>
+        <v>-5.073700000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>2.688700000000001</v>
+        <v>2.6887</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6909999999999989</v>
+        <v>-0.6909999999999998</v>
       </c>
       <c r="I13" t="n">
         <v>3.379700000000001</v>
@@ -1456,7 +1456,7 @@
         <v>-11.3861</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8925000000000001</v>
+        <v>0.8924999999999998</v>
       </c>
       <c r="P13" t="n">
         <v>-3.8616</v>
@@ -1468,28 +1468,28 @@
         <v>16.4117</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.275300000000001</v>
+        <v>-3.7233</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1345</v>
+        <v>0.6867000000000001</v>
       </c>
       <c r="U13" t="n">
         <v>-4.409800000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8569000000000006</v>
+        <v>-0.8569000000000001</v>
       </c>
       <c r="W13" t="n">
         <v>5.724899999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.5818</v>
+        <v>-6.581799999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>M. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3512</v>
+        <v>4.1656</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7457</v>
+        <v>2.4251</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6056</v>
+        <v>1.7405</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0142</v>
+        <v>-1.1856</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4755</v>
+        <v>-0.3447</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4897</v>
+        <v>-0.8409</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5397</v>
+        <v>0.1539</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2335</v>
+        <v>1.0354</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7732</v>
+        <v>-0.8815</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5255</v>
+        <v>-1.3395</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.242</v>
+        <v>-1.3801</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7165</v>
+        <v>0.0406</v>
       </c>
       <c r="P14" t="n">
-        <v>2.8962</v>
+        <v>2.7031</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8962</v>
+        <v>2.7031</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7264</v>
+        <v>1.4204</v>
       </c>
       <c r="T14" t="n">
-        <v>2.206</v>
+        <v>0.758</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4796</v>
+        <v>0.6625</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X14" t="n">
         <v>-0.2856</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. YOUNG MEDIERO</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7934</v>
+        <v>4.121</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2183</v>
+        <v>1.8149</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5751</v>
+        <v>2.3061</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1856</v>
+        <v>0.0142</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3447</v>
+        <v>-1.4755</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8409</v>
+        <v>1.4897</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1539</v>
+        <v>0.5397</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0354</v>
+        <v>-0.2335</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.8815</v>
+        <v>0.7732</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3395</v>
+        <v>-0.5255</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3801</v>
+        <v>-1.242</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0406</v>
+        <v>0.7165</v>
       </c>
       <c r="P15" t="n">
-        <v>2.7031</v>
+        <v>2.8962</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7031</v>
+        <v>2.8962</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0482</v>
+        <v>1.4962</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5511</v>
+        <v>1.2752</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4971</v>
+        <v>0.221</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2277</v>
+        <v>-0.2856</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>-0.2856</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7746</v>
+        <v>4.0641</v>
       </c>
       <c r="E16" t="n">
         <v>3.058</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7166</v>
+        <v>1.0061</v>
       </c>
       <c r="G16" t="n">
         <v>0.5884</v>
@@ -1702,13 +1702,13 @@
         <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6069</v>
+        <v>0.8965</v>
       </c>
       <c r="T16" t="n">
         <v>0.4963</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1107</v>
+        <v>0.4002</v>
       </c>
       <c r="V16" t="n">
         <v>1.2277</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2798</v>
+        <v>3.2068</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7786</v>
+        <v>2.4683</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5012</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>2.3643</v>
@@ -1780,13 +1780,13 @@
         <v>1.5446</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6452</v>
+        <v>0.5722</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8547</v>
+        <v>0.5444</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2095</v>
+        <v>0.0278</v>
       </c>
       <c r="V17" t="n">
         <v>0.6565</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5641</v>
+        <v>2.1584</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.247</v>
+        <v>0.2701</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8112</v>
+        <v>1.8883</v>
       </c>
       <c r="G18" t="n">
         <v>0.652</v>
@@ -1858,13 +1858,13 @@
         <v>2.8962</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3642</v>
+        <v>0.9584</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.028</v>
+        <v>0.4891</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3922</v>
+        <v>0.4693</v>
       </c>
       <c r="V18" t="n">
         <v>1.5133</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8495</v>
+        <v>1.2521</v>
       </c>
       <c r="E19" t="n">
         <v>1.6189</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7694</v>
+        <v>-0.3668</v>
       </c>
       <c r="G19" t="n">
         <v>0.6977</v>
@@ -1936,13 +1936,13 @@
         <v>2.1239</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2869</v>
+        <v>0.6895</v>
       </c>
       <c r="T19" t="n">
         <v>-0.08309999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.37</v>
+        <v>0.7726</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3282</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BECERRA ORDOÑEZ</t>
+          <t>J. JIMENEZ LAHOZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5138</v>
+        <v>0.9764</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2206</v>
+        <v>-0.7811</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7067</v>
+        <v>1.7574</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1372</v>
+        <v>1.3019</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6345</v>
+        <v>-0.2965</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4974</v>
+        <v>1.5983</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0892</v>
+        <v>2.1099</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0485</v>
+        <v>0.3939</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0407</v>
+        <v>1.7159</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9520999999999999</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.414</v>
+        <v>-0.6904</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5381</v>
+        <v>-0.1176</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3515</v>
+        <v>2.3169</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0441</v>
+        <v>-0.0552</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1655</v>
+        <v>-0.3037</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1215</v>
+        <v>0.2485</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2277</v>
+        <v>-0.6565</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. ELTING</t>
+          <t>J. BECERRA ORDOÑEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0047</v>
+        <v>0.6959</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0697</v>
+        <v>1.4274</v>
       </c>
       <c r="F21" t="n">
-        <v>0.07439999999999999</v>
+        <v>-0.7316</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1664</v>
+        <v>1.1372</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2071</v>
+        <v>1.6345</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0407</v>
+        <v>-0.4974</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0407</v>
+        <v>2.0892</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2.0485</v>
       </c>
       <c r="L21" t="n">
         <v>0.0407</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2071</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2071</v>
+        <v>-0.414</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.5381</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1931</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.022</v>
+        <v>0.1379</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1104</v>
+        <v>0.0413</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LAHOZ</t>
+          <t>B. ELTING</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3862</v>
+        <v>-0.0698</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1947</v>
+        <v>-0.0697</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8085</v>
+        <v>-0.0001</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3019</v>
+        <v>-0.1664</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2965</v>
+        <v>-0.2071</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5983</v>
+        <v>0.0407</v>
       </c>
       <c r="J22" t="n">
-        <v>2.1099</v>
+        <v>0.0407</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3939</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.7159</v>
+        <v>0.0407</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8080000000000001</v>
+        <v>-0.2071</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6904</v>
+        <v>-0.2071</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1176</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3169</v>
+        <v>0.1931</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4178</v>
+        <v>-0.0965</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7174</v>
+        <v>-0.1104</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7004</v>
+        <v>0.0139</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1999</v>
+        <v>-4.298</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4598</v>
+        <v>-3.0461</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7401</v>
+        <v>-1.2519</v>
       </c>
       <c r="G23" t="n">
         <v>-2.029</v>
@@ -2248,13 +2248,13 @@
         <v>1.1585</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5571</v>
+        <v>0.3448</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3311</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.226</v>
+        <v>0.2622</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8415</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.2403</v>
+        <v>-6.5201</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.595</v>
+        <v>-4.1121</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6452</v>
+        <v>-2.408</v>
       </c>
       <c r="G24" t="n">
         <v>-6.0635</v>
@@ -2326,13 +2326,13 @@
         <v>1.7377</v>
       </c>
       <c r="S24" t="n">
-        <v>1.6381</v>
+        <v>1.3583</v>
       </c>
       <c r="T24" t="n">
-        <v>1.7372</v>
+        <v>1.2201</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0.1381</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6565</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.304700000000001</v>
+        <v>9.752400000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>5.073899999999998</v>
+        <v>5.073700000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2312</v>
+        <v>4.6784</v>
       </c>
       <c r="G25" t="n">
         <v>-2.688800000000001</v>
@@ -2392,7 +2392,7 @@
         <v>-10.6951</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.4875</v>
+        <v>-2.487500000000001</v>
       </c>
       <c r="P25" t="n">
         <v>3.861599999999999</v>
@@ -2404,19 +2404,19 @@
         <v>20.2732</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2749</v>
+        <v>7.7225</v>
       </c>
       <c r="T25" t="n">
         <v>4.409800000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1347000000000001</v>
+        <v>3.3127</v>
       </c>
       <c r="V25" t="n">
-        <v>0.8569000000000003</v>
+        <v>0.8568999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>6.581799999999999</v>
+        <v>6.5818</v>
       </c>
       <c r="X25" t="n">
         <v>-5.7249</v>
